--- a/04 - RELATÓRIO DE PAGAMENTO/Municipios.xlsx
+++ b/04 - RELATÓRIO DE PAGAMENTO/Municipios.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuário 1\Documents\Inovve_Automação\02 - DOCUMENTOS\RELATÓRIO DE PAGAMENTO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuário 1\Documents\Inovve_Automação\04 - RELATÓRIO DE PAGAMENTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3374AD02-6909-4240-8E64-3C748B86CAA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0006A663-E992-458B-93C8-9ADEFD6B29CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="27">
   <si>
     <t>Município</t>
   </si>
@@ -103,6 +103,9 @@
   </si>
   <si>
     <t>Catolé do Rocha</t>
+  </si>
+  <si>
+    <t>São Mamede</t>
   </si>
 </sst>
 </file>
@@ -434,7 +437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.5546875" customWidth="1"/>
@@ -639,6 +642,20 @@
         <v>7</v>
       </c>
     </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/04 - RELATÓRIO DE PAGAMENTO/Municipios.xlsx
+++ b/04 - RELATÓRIO DE PAGAMENTO/Municipios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuário 1\Documents\Inovve_Automação\04 - RELATÓRIO DE PAGAMENTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0006A663-E992-458B-93C8-9ADEFD6B29CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{042AB01D-E4A7-4D99-A6F4-6A74B909533C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="28">
   <si>
     <t>Município</t>
   </si>
@@ -106,6 +106,9 @@
   </si>
   <si>
     <t>São Mamede</t>
+  </si>
+  <si>
+    <t>Araruna</t>
   </si>
 </sst>
 </file>
@@ -437,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.5546875" customWidth="1"/>
@@ -656,6 +659,20 @@
         <v>7</v>
       </c>
     </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
